--- a/data/trans_orig/IP31A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>28382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30460</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>39440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>36129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72578</t>
+          <t>71136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81983</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110338</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127687</t>
+          <t>127237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151304</t>
+          <t>150655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148117</t>
+          <t>149055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258951</t>
+          <t>257453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292071</t>
+          <t>292670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>51093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38802</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57989</t>
+          <t>58101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>47315</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64654</t>
+          <t>64506</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91747</t>
+          <t>93108</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116986</t>
+          <t>118875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49082</t>
+          <t>50208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61996</t>
+          <t>63322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86063</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27095</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>49409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73535</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65724</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85595</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77951</t>
+          <t>79553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100546</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148568</t>
+          <t>150183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>179755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>58647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78808</t>
+          <t>79338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>35263</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98875</t>
+          <t>98060</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>126003</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77144</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>129962</t>
+          <t>128794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>162635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>216187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>258192</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>277982</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>317411</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>290545</t>
+          <t>289380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330352</t>
+          <t>330766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>580239</t>
+          <t>581618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>636357</t>
+          <t>636317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145592</t>
+          <t>145990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179385</t>
+          <t>180674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121191</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154309</t>
+          <t>156329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>275191</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>324054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51239</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>41116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60612</t>
+          <t>61090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>43087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>66132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86142</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25009</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40747</t>
+          <t>40443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48629</t>
+          <t>47334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60896</t>
+          <t>60186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74473</t>
+          <t>74350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103041</t>
+          <t>101798</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108435</t>
+          <t>107660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131743</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>127571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153519</t>
+          <t>154304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243338</t>
+          <t>241164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278790</t>
+          <t>278695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39413</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60199</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88693</t>
+          <t>88536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118207</t>
+          <t>116336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21381</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49966</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68943</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>85272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141030</t>
+          <t>141735</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>168393</t>
+          <t>169919</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41684</t>
+          <t>41376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84167</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39927</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33014</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52673</t>
+          <t>51543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72824</t>
+          <t>72173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69327</t>
+          <t>69530</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>91445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127214</t>
+          <t>127626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156461</t>
+          <t>155047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>48216</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68147</t>
+          <t>67746</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52251</t>
+          <t>52064</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86296</t>
+          <t>87979</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114173</t>
+          <t>113954</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30560</t>
+          <t>30565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114402</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>150184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200103</t>
+          <t>198261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>244383</t>
+          <t>242770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>274558</t>
+          <t>274571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315817</t>
+          <t>314002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>315919</t>
+          <t>316588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358500</t>
+          <t>357465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>604219</t>
+          <t>604640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>660975</t>
+          <t>658406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147506</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>124118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158929</t>
+          <t>159274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284380</t>
+          <t>282586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>331643</t>
+          <t>332522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>77721</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42886</t>
+          <t>43318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44214</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42662</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82054</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>36842</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>45412</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65693</t>
+          <t>67370</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>91775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112592</t>
+          <t>113892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126458</t>
+          <t>126138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150670</t>
+          <t>150925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224556</t>
+          <t>224941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258820</t>
+          <t>257550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61903</t>
+          <t>61938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>48317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95549</t>
+          <t>96452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125929</t>
+          <t>126099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>39664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86638</t>
+          <t>86552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108603</t>
+          <t>106961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74160</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95986</t>
+          <t>96408</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>167606</t>
+          <t>167400</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196210</t>
+          <t>197399</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37783</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57028</t>
+          <t>56629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76972</t>
+          <t>76660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104096</t>
+          <t>103160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43556</t>
+          <t>44139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>83029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64523</t>
+          <t>64754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85638</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133252</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163034</t>
+          <t>162726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>55969</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>59785</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81883</t>
+          <t>83034</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109561</t>
+          <t>109795</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>23560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>37517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98856</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>163794</t>
+          <t>164429</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>290351</t>
+          <t>290461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>331169</t>
+          <t>328551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312317</t>
+          <t>312503</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>353543</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>615312</t>
+          <t>615551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>670914</t>
+          <t>672474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>147562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184975</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>298482</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>348133</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80365</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>111073</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
